--- a/lecNote/01_python/0710_ch10_11.xlsx
+++ b/lecNote/01_python/0710_ch10_11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\01_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB7028D-0448-4E5A-AEBF-CE629A152B6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E97314-FFF1-4575-9D20-8349FDBFBD00}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" activeTab="3" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
   </bookViews>
   <sheets>
     <sheet name="비트" sheetId="1" r:id="rId1"/>
@@ -439,7 +439,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -485,25 +485,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -839,28 +842,28 @@
       <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>41</v>
       </c>
     </row>
@@ -883,28 +886,28 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="19">
-        <v>1</v>
-      </c>
-      <c r="K2" s="20">
-        <v>0</v>
-      </c>
-      <c r="L2" s="20">
-        <v>0</v>
-      </c>
-      <c r="M2" s="20">
-        <v>0</v>
-      </c>
-      <c r="N2" s="20">
-        <v>0</v>
-      </c>
-      <c r="O2" s="20">
-        <v>0</v>
-      </c>
-      <c r="P2" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="21">
+      <c r="J2" s="17">
+        <v>1</v>
+      </c>
+      <c r="K2" s="18">
+        <v>0</v>
+      </c>
+      <c r="L2" s="18">
+        <v>0</v>
+      </c>
+      <c r="M2" s="18">
+        <v>0</v>
+      </c>
+      <c r="N2" s="18">
+        <v>0</v>
+      </c>
+      <c r="O2" s="18">
+        <v>0</v>
+      </c>
+      <c r="P2" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="19">
         <v>0</v>
       </c>
     </row>
@@ -1702,12 +1705,12 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="20" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="5">
         <v>0</v>
       </c>
@@ -1765,7 +1768,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5">
@@ -1794,7 +1797,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="5">
         <v>0</v>
       </c>
@@ -2059,7 +2062,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="2">
+      <c r="B2" s="22">
         <v>0</v>
       </c>
       <c r="C2" s="2">
@@ -2070,7 +2073,7 @@
         <f>C2*C2</f>
         <v>100</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="22">
         <v>8</v>
       </c>
       <c r="F2" s="2">
@@ -2083,7 +2086,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="2">
+      <c r="B3" s="22">
         <v>0</v>
       </c>
       <c r="C3" s="2">
@@ -2094,7 +2097,7 @@
         <f t="shared" ref="D3:D6" si="1">C3*C3</f>
         <v>100</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="22">
         <v>8.5</v>
       </c>
       <c r="F3" s="2">
@@ -2107,18 +2110,18 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
-        <v>10</v>
+      <c r="B4" s="22">
+        <v>2</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
+        <v>64</v>
+      </c>
+      <c r="E4" s="22">
         <v>9</v>
       </c>
       <c r="F4" s="2">
@@ -2131,7 +2134,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
+      <c r="B5" s="22">
         <v>18</v>
       </c>
       <c r="C5" s="2">
@@ -2142,7 +2145,7 @@
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="22">
         <v>9.5</v>
       </c>
       <c r="F5" s="2">
@@ -2155,18 +2158,18 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
-        <v>22</v>
+      <c r="B6" s="22">
+        <v>30</v>
       </c>
       <c r="C6" s="2">
         <f t="shared" si="0"/>
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-      <c r="E6" s="2">
+        <v>400</v>
+      </c>
+      <c r="E6" s="22">
         <v>10</v>
       </c>
       <c r="F6" s="2">
@@ -2192,7 +2195,7 @@
       </c>
       <c r="D7" s="12">
         <f t="shared" si="4"/>
-        <v>81.599999999999994</v>
+        <v>145.6</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="4"/>
@@ -2216,7 +2219,7 @@
       </c>
       <c r="D8" s="14">
         <f>SQRT(D7)</f>
-        <v>9.0332718325089711</v>
+        <v>12.066482503198685</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
@@ -2228,5 +2231,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>